--- a/Template Catatan Bulanan - VhannyLobster.xlsx
+++ b/Template Catatan Bulanan - VhannyLobster.xlsx
@@ -71,7 +71,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -93,11 +93,17 @@
         <color rgb="00D1D5DB"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -118,6 +124,14 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -663,7 +677,6 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -795,7 +808,6 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -898,7 +910,6 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -960,152 +971,202 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Salatiga</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Salatiga (hidup)</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="n">
         <v>130</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
+      <c r="C2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="10">
         <f>B2+C2-D2-E2</f>
         <v/>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Lobster hidup</t>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>Lobster hidup, sisa batch 300kg</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Boyolali</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Boyolali (hidup)</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="n">
         <v>145</v>
       </c>
-      <c r="C3" s="7" t="n">
-        <v>250</v>
-      </c>
-      <c r="D3" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="C3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="10">
         <f>B3+C3-D3-E3</f>
         <v/>
       </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>145 hidup + 250 frozen</t>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Lobster hidup, sisa batch 400kg</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Jogja</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Boyolali (frozen baru)</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>250</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="10">
         <f>B4+C4-D4-E4</f>
         <v/>
       </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Lobster hidup</t>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Pembelian 26 Jul, 250kg frozen</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Bekasi</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="6">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Jogja (hidup)</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="10">
         <f>B5+C5-D5-E5</f>
         <v/>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Fresh/frozen</t>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Lobster hidup, sisa batch 19kg</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Bekasi (fresh/frozen)</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11">
+        <f>B6+C6-D6-E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Sisa dari 30kg. 2kg frozen terjual 27 Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Campuran (mati/frozen)</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="10">
+        <f>B7+C7-D7-E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Harga jual diskon Rp 180rb/kg. 6kg terjual 26 Jul. Sisa 25kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B6" s="9">
-        <f>SUM(B2:B5)</f>
+      <c r="B8" s="13">
+        <f>SUM(B2:B7)</f>
         <v/>
       </c>
-      <c r="C6" s="9">
-        <f>SUM(C2:C5)</f>
+      <c r="C8" s="13">
+        <f>SUM(C2:C7)</f>
         <v/>
       </c>
-      <c r="D6" s="9">
-        <f>SUM(D2:D5)</f>
+      <c r="D8" s="13">
+        <f>SUM(D2:D7)</f>
         <v/>
       </c>
-      <c r="E6" s="9">
-        <f>SUM(E2:E5)</f>
+      <c r="E8" s="13">
+        <f>SUM(E2:E7)</f>
         <v/>
       </c>
-      <c r="F6" s="9">
-        <f>SUM(F2:F5)</f>
+      <c r="F8" s="13">
+        <f>SUM(F2:F7)</f>
         <v/>
       </c>
-      <c r="G6" s="9">
-        <f>SUM(G2:G5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>PETUNJUK:</t>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Stok akhir otomatis</t>
         </is>
       </c>
     </row>

--- a/Template Catatan Bulanan - VhannyLobster.xlsx
+++ b/Template Catatan Bulanan - VhannyLobster.xlsx
@@ -994,7 +994,7 @@
       </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>Lobster hidup, sisa batch 300kg</t>
+          <t>Lobster hidup</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F3" s="10">
         <f>B3+C3-D3-E3</f>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>Lobster hidup, sisa batch 400kg</t>
+          <t>31kg mati → pindah ke campuran. Sisa 114kg hidup</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>Pembelian 26 Jul, 250kg frozen</t>
+          <t>Pembelian 26 Jul</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Lobster hidup, sisa batch 19kg</t>
+          <t>Lobster hidup</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>Sisa dari 30kg. 2kg frozen terjual 27 Jul</t>
+          <t>2kg frozen terjual 27 Jul</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>Harga jual diskon Rp 180rb/kg. 6kg terjual 26 Jul. Sisa 25kg</t>
+          <t>Dari Boyolali. 6kg terjual 26 Jul. Sisa 25kg @Rp180rb</t>
         </is>
       </c>
     </row>
@@ -1164,11 +1164,7 @@
         <f>SUM(F2:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>Stok akhir otomatis</t>
-        </is>
-      </c>
+      <c r="G8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">

--- a/Template Catatan Bulanan - VhannyLobster.xlsx
+++ b/Template Catatan Bulanan - VhannyLobster.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,29 +32,16 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00888888"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="00666666"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -71,7 +58,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -93,45 +80,22 @@
         <color rgb="00D1D5DB"/>
       </bottom>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -498,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -506,10 +470,10 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,140 +504,802 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Status Bayar</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>No. Invoice</t>
+          <t>No Invoice</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Akun</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Keterangan</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Bukti Foto</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Cici (eceran)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>6</v>
+          <t>Penjualan ke Hakka Restoran</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>180000</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1080000</v>
+        <v>3600000</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>lunas</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>6kg mati campuran</t>
+          <t>Penjualan — Restoran</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>foto.jpg</t>
+          <t>Dari batch Salatiga 40kg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Eceran</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>2</v>
+          <t>Penjualan ke Hakka Restoran</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>60</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>180000</v>
       </c>
       <c r="E3" s="3" t="n">
+        <v>10800000</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Restoran</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Dari batch Salatiga 300kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan ke Hakka Restoran</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>190000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Restoran</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Dari batch Salatiga 40kg, ukuran 50gr</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan eceran</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>450000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Eceran</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Cash lunas. Dari batch Jogja</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Dollar/Ekspor</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Dibayar dollar, dari batch Salatiga 300kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>165000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>11200000</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Dollar/Ekspor</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Susut 7kg dari 75kg. Dibayar dollar. Dari batch Boyolali 400kg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan ke Hakka Restoran</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Restoran</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Dari sisa Salatiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan ke Hakka Restoran</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>450000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>INV00006</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Restoran</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan ke Hakka Restoran</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>165000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Restoran</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Campuran</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan eceran</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>450000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>900000</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Eceran</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Campuran</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan ke Hakka Restoran</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>2520000</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>INV00009</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Restoran</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan eceran</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>450000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>450000</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Eceran</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan ke Hakka Restoran</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>185000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>33300000</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>tempo</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>INV00008</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Restoran</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Tempo 10 hari (28 Jul). Sisa tagihan Rp 33.300.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan eceran</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>160000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>320000</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Eceran</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Campuran</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan ke Hakka Restoran</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>165000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>2475000</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>INV00010</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Restoran</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan ke Hakka Restoran</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>600000</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>INV00011</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Restoran</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Lunas. File tertulis INV00010, seharusnya INV00011. Frozen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan ke Hakka Restoran</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>720000</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Restoran</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan eceran</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E19" s="3" t="n">
         <v>360000</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>lunas</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>2kg frozen Bekasi</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>foto.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>PETUNJUK:</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>• Isi setiap transaksi, maks 2-3 hari setelah terjadi</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>• Status Bayar: lunas / tempo / dp</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>• Foto: kirim via WA bersamaan, isi nama file di kolom ini</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>• Baris contoh bisa ditimpa dengan data asli</t>
-        </is>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Eceran</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan eceran</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>720000</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Eceran</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan eceran</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1080000</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Eceran</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Harga diskon (mati), normal Rp 400rb/kg. Dari 31kg mati campuran.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan eceran</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>360000</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Penjualan — Eceran</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Harga diskon (frozen). Stok existing Bekasi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>97505000</v>
       </c>
     </row>
   </sheetData>
@@ -688,16 +1314,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -734,7 +1360,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Status Bayar</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -746,65 +1372,437 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Petani Boyolali (multi)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+          <t>Plastik bungkus</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="3" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>hidup</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Pembelian lobster Salatiga</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>hidup</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Dijual 20kg @ Rp 180.000 + 20kg @ Rp 190.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Kebutuhan perjalanan Boyolali</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>hidup</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Pembelian lobster Salatiga</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>115000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>hidup</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>dp</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>DP Rp 20.050.000, sisa Rp 14.450.000. Dijual 60kg &amp; 100kg (dollar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Pembelian lobster Bekasi</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>140000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>2328000</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>frozen</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Ukuran 30-40gr. 6kg dibuang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Stiker1 200 pcs (label packing</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="3" t="n">
+        <v>196000</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>hidup</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Pembelian lobster Jogja</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>173000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>3225000</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>hidup</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Dijual 4kg @ Rp 450.000 = Rp 1.800.000 (lunas). 15kg sisa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Pembelian lobster Boyolali</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>46000000</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>hidup</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>dp</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>DP Rp 17.000.000, hutang Rp 29.000.000. 68kg jual dollar. 180kg dibawa ke Salatiga.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Stiker2 250 pcs (label packing</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="3" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>hidup</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Pembelian lobster Boyolali</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>130000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>hidup</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Pembelian lobster Boyolali</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>130000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>20150000</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>hidup</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Sekali bayar termasuk packing Rp 250.000. Lunas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Pembelian lobster Boyolali (ca</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="3" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>930000</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>hidup</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Pembelian lobster Boyolali frozen</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>79540</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>19885000</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>frozen</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>dp</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>250kg frozen, DP 10jt</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>PETUNJUK:</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>• Isi setiap kali beli lobster</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>• Jenis: hidup / frozen / campuran</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>• Status: lunas (lunas semua), dp (bayar sebagian), tempo (bayar nanti)</t>
-        </is>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>DP Rp 10.000.000 dari setoran modal owner, sisa Rp 9.885.000 dari profit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>133339000</v>
       </c>
     </row>
   </sheetData>
@@ -819,14 +1817,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -852,61 +1850,168 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Bukti Foto</t>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Konsumsi Tenaga Kerja</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Makanan, rokok untuk pekerja</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>404000</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>Tenaga Kerja</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Bayar tukang</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Denda &amp; Tilang</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Kena tilang</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Biaya Lain-lain</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Materai</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Tenaga Kerja</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Tukang packing</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>450000</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>foto.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>PETUNJUK:</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>• Semua pengeluaran di luar pembelian lobster</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>• Kategori: pilih dari dropdown atau tulis manual</t>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>• Lampirkan foto bukti (struk, nota, transfer)</t>
-        </is>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Biaya Sewa</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Beban Sewa Juli 2026 (1/7)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>10714285</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>12268285</v>
       </c>
     </row>
   </sheetData>
@@ -921,16 +2026,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -941,27 +2046,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Stok Awal (kg)</t>
+          <t>Stok Awal</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Masuk (kg)</t>
+          <t>Masuk</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Terjual (kg)</t>
+          <t>Terjual</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Mati (kg)</t>
+          <t>Mati</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Stok Akhir (kg)</t>
+          <t>Stok Akhir</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -971,219 +2076,116 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Salatiga (hidup)</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n">
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="C2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="10">
-        <f>B2+C2-D2-E2</f>
-        <v/>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>Lobster hidup</t>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Sisa batch 300kg</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Boyolali (hidup)</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n">
-        <v>145</v>
-      </c>
-      <c r="C3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>31</v>
-      </c>
-      <c r="F3" s="10">
-        <f>B3+C3-D3-E3</f>
-        <v/>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>31kg mati → pindah ke campuran. Sisa 114kg hidup</t>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Sisa batch 400kg, deduct 31kg mati (pindah ke campuran)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Boyolali (frozen baru)</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="11" t="n">
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="D4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="10">
-        <f>B4+C4-D4-E4</f>
-        <v/>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Pembelian 26 Jul</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Jogja (hidup)</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="10">
-        <f>B5+C5-D5-E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>Lobster hidup</t>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Sisa batch 19kg</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Bekasi (fresh/frozen)</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="11">
-        <f>B6+C6-D6-E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>2kg frozen terjual 27 Jul</t>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Sisa dari 30kg. 6kg dibuang, 2kg frozen terjual 27 Jul @ Rp 180rb.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Campuran (mati/frozen)</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="11" t="n">
-        <v>31</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="10">
-        <f>B7+C7-D7-E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>Dari Boyolali. 6kg terjual 26 Jul. Sisa 25kg @Rp180rb</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B8" s="13">
-        <f>SUM(B2:B7)</f>
-        <v/>
-      </c>
-      <c r="C8" s="13">
-        <f>SUM(C2:C7)</f>
-        <v/>
-      </c>
-      <c r="D8" s="13">
-        <f>SUM(D2:D7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="13">
-        <f>SUM(E2:E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="13">
-        <f>SUM(F2:F7)</f>
-        <v/>
-      </c>
-      <c r="G8" s="12" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>• Update setiap ada transaksi (jual/beli/mati)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>• Stok Akhir otomatis = Stok Awal + Masuk - Terjual - Mati</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>• Kalau bingung asal stok, tulis di Keterangan</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Campuran (mati/frozen — diskon)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Dari 31kg mati (deduct Boyolali). 6kg terjual 26 Jul @ Rp 180rb, sisa 25kg. Harga normal Rp 400rb/kg.</t>
         </is>
       </c>
     </row>
